--- a/deliverables/积石山县6.2级地震应急处置报告-推演数据表.xlsx
+++ b/deliverables/积石山县6.2级地震应急处置报告-推演数据表.xlsx
@@ -1,43 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_数据引用索引" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="R01_灾害分级与响应推演" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="R02_路线效用计算" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="R03_资源需求缺口总表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="R04_次生地质灾害推演" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="R05_口径冲突台账" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="R06_待补数据清单" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="01_地理节点" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="02_车辆与载荷" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="03_路径推演" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="04_搜救调度" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="05_医疗救治" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="06_群众安置" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="07_基础设施抢修" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="08_图谱推演规则" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="09_推演函数" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="10_求解器与算法" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="11_算法参数" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="12_求解结果" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="13_推演步骤" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="需求函数库_补齐" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="资源需求测算_补齐" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="数据引用追踪_补齐" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="推演步骤_补齐" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="07_本体对象字典" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="08_本体关系与推理规则" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="09_灾情推演函数库" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="10_完整资源需求函数库" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="11_求解变量与目标函数" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="12_约束函数库" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="13_Agent_Skill_MCP" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="14_动态GraphPatch规则" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_数据引用索引" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R01_灾害分级与响应推演" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R02_路线效用计算" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R03_资源需求缺口总表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R04_次生地质灾害推演" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R05_口径统一裁决表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R06_补齐数据取值表" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_地理节点" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_车辆与载荷" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_路径推演" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_搜救调度" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_医疗救治" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_群众安置" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_基础设施抢修" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_图谱推演规则" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_推演函数" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_求解器与算法" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_算法参数" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_求解结果" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_推演步骤" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求函数库_补齐" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="资源需求测算_补齐" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据引用追踪_补齐" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="推演步骤_补齐" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_本体对象字典" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_本体关系与推理规则" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_灾情推演函数库" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_完整资源需求函数库" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_求解变量与目标函数" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_约束函数库" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Agent_Skill_MCP" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_动态GraphPatch规则" sheetId="32" state="visible" r:id="rId32"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -79,7 +79,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -104,6 +104,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -134,7 +139,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,6 +161,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
@@ -1168,10 +1176,10 @@
       <c r="H2" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="9" t="n">
+      <c r="I2" s="10" t="n">
         <v>68</v>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>第1位</t>
         </is>
@@ -1218,10 +1226,10 @@
       <c r="H3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I3" s="9" t="n">
+      <c r="I3" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>第6位</t>
         </is>
@@ -1268,10 +1276,10 @@
       <c r="H4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I4" s="9" t="n">
+      <c r="I4" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>第4位</t>
         </is>
@@ -1318,10 +1326,10 @@
       <c r="H5" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="I5" s="9" t="n">
+      <c r="I5" s="10" t="n">
         <v>39.5</v>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>第5位</t>
         </is>
@@ -1368,10 +1376,10 @@
       <c r="H6" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I6" s="9" t="n">
+      <c r="I6" s="10" t="n">
         <v>67</v>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>第2位</t>
         </is>
@@ -1418,10 +1426,10 @@
       <c r="H7" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="9" t="n">
+      <c r="I7" s="10" t="n">
         <v>64.5</v>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>第3位</t>
         </is>
@@ -3431,14 +3439,14 @@
           <t>目标500人；现有320人</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>路线效用函数外的缺口函数 Gap=MAX(0,500−320)</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>180人</t>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>Gap=MAX(0,500−320)</t>
+        </is>
+      </c>
+      <c r="D2" s="11" t="inlineStr">
+        <is>
+          <t>180人；首轮编成A150+B100+孤岛70=320，增援后A180+B140+孤岛90+机动90=500</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -3458,14 +3466,14 @@
           <t>目标80辆；现有58辆</t>
         </is>
       </c>
-      <c r="C3" s="10" t="inlineStr">
-        <is>
-          <t>Gap=MAX(0,80−58)</t>
-        </is>
-      </c>
-      <c r="D3" s="10" t="inlineStr">
-        <is>
-          <t>22辆</t>
+      <c r="C3" s="11" t="inlineStr">
+        <is>
+          <t>Gap=MAX(0,80−46)</t>
+        </is>
+      </c>
+      <c r="D3" s="11" t="inlineStr">
+        <is>
+          <t>34辆（县域18+州级16+省级12=46）</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -3485,14 +3493,14 @@
           <t>目标330张；现有210张</t>
         </is>
       </c>
-      <c r="C4" s="10" t="inlineStr">
-        <is>
-          <t>Gap=MAX(0,330−210)</t>
-        </is>
-      </c>
-      <c r="D4" s="10" t="inlineStr">
-        <is>
-          <t>120张</t>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Gap=MAX(0,330−110) 县域；MAX(0,330−250) 全域</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>县域缺口220张；全域缺口80张</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -3512,14 +3520,14 @@
           <t>计划安置3600人</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>WaterDemand=3600×15L</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>54000升/日 = 54 m³/日</t>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>WaterDemand=3750×15L</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>56250升/日 = 56.25 m³/日</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -3539,14 +3547,14 @@
           <t>计划安置3300人</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>WaterDemand=3300×15L</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>49500升/日 = 49.5 m³/日</t>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>WaterDemand=3450×15L</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>51750升/日 = 51.75 m³/日</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -3566,12 +3574,12 @@
           <t>需求54m³；10辆供水车；12m³/辆</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>Trips=CEILING(54÷(10×12))</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>Trips=CEILING(56.25÷(10×12))</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>1趟</t>
         </is>
@@ -3593,12 +3601,12 @@
           <t>重伤116人；18辆；2人/车次</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>AmbulanceTrips=CEILING(116÷(18×2))</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D8" s="11" t="inlineStr">
         <is>
           <t>4批</t>
         </is>
@@ -3620,14 +3628,14 @@
           <t>28km；48min；道路风险2；通行4；边坡2</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="11" t="inlineStr">
         <is>
           <t>RouteScore=100−0.5×48−8×2+6×4−8×2</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>68分</t>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>68分（第1位）</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -3647,14 +3655,14 @@
           <t>31km；62min；道路风险3；通行3；边坡4</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>RouteScore=100−0.5×62−8×3+6×3−8×4</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>31分</t>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>31分（第6位，须侦检后放行）</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -3674,21 +3682,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>说明：地震线与次生地质灾害线的级别并列成立，严禁互相换算（DEC-15）。分级应对与响应分级是两个独立维度，不可互推（DEC-LX-08）。</t>
+          <t>本表为单一口径。分级应对与响应分级是两个独立维度，分别输出，不可互推。</t>
         </is>
       </c>
     </row>
@@ -3720,7 +3728,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>置信度</t>
+          <t>数据类别</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3740,17 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>积石山县总人口278089人；面积909.97 km²</t>
+          <t>总人口278089人；面积909.97 km²；口径取按行政区计算</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>278089÷909.97 = 305.6 人/km² &gt; 200 人/km²</t>
+          <t>278089÷909.97 = 305.6 &gt; 200 人/km²</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>成立——落入震级判据区域</t>
+          <t>成立</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -3750,16 +3758,16 @@
           <t>临夏州地震应急预案§3.1；DEC-LX-03</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>推算（口径待州地震局确认，C-LX-11）</t>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>震级支路定级</t>
+          <t>震级支路</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -3769,7 +3777,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>6.2 落入「6.0级以上、7.0级以下」</t>
+          <t>落入6.0以上、7.0以下</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -3779,7 +3787,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>临夏州地震应急预案§3.1</t>
+          <t>§3.1</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -3791,32 +3799,32 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>伤亡支路定级</t>
+          <t>伤亡支路</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>死亡失踪数：简报未给（失联待搜寻24人）</t>
+          <t>确认死亡0人，失联待搜寻24人</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>死亡失踪&lt;10 → 一般（Ⅳ级）；伤亡回传后须复判</t>
+          <t>死亡失踪&lt;10</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>暂为Ⅳ级，取两支路更高者</t>
+          <t>一般（Ⅳ级）；回传后复判</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>临夏州地震应急预案§3.1</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>待核</t>
+          <t>§3.1</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
@@ -3828,12 +3836,12 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>震级支路Ⅱ级 / 伤亡支路Ⅳ级</t>
+          <t>两支路取高</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>取更高者</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -3843,7 +3851,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>§3.1；rule RULE-LX-GRADE</t>
+          <t>§3.1</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
@@ -3855,17 +3863,17 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>分级应对（谁负责）</t>
+          <t>分级应对</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>重大地震灾害</t>
+          <t>重大</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>MAP(重大→省抗震救灾指挥部)</t>
+          <t>MAP(重大→省)</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -3875,24 +3883,24 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>临夏州地震应急预案§3.2.1</t>
+          <t>§3.2.1</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>响应分级（启动哪级）</t>
+          <t>响应分级</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>重大地震灾害</t>
+          <t>重大</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -3907,12 +3915,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>临夏州地震应急预案§5.2</t>
+          <t>§5.2</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3937,7 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>州抗震救灾指挥部提出建议→报州委州政府→州政府决定启动</t>
+          <t>指挥部建议→报州委州政府→州政府决定</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -3939,12 +3947,12 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>§5.2；DEC-07/DEC-LX-01</t>
+          <t>§5.2</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3984,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -3993,12 +4001,12 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>立即成立州抗震救灾现场指挥部</t>
+          <t>立即成立</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>应成立；指挥长由总指挥或州委州政府指定专人</t>
+          <t>应成立</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -4008,7 +4016,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -4020,12 +4028,12 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>积石山为保安族东乡族撒拉族自治县</t>
+          <t>民族自治县+深夜+高海拔冻融+Ⅷ度</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>少数民族聚居地区可适当提高响应级别</t>
+          <t>§3.2.2 提级条款</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
@@ -4047,128 +4055,64 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>上报要求</t>
+          <t>速报时限</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Ⅱ级</t>
+          <t>Ⅱ级（大型口径）</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>第一时间向省委、省政府报告</t>
+          <t>30分钟速报；书面≤事发后2小时</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>必须</t>
+          <t>30分钟 / 2小时</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>§5.2</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>原文直述</t>
+          <t>积石山县地质灾害预案§4.1；DEC-LX-06</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>速报时限</t>
+          <t>震情速报阈值</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Ⅱ级（大型口径）</t>
+          <t>农村地区≥4.0级</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>30分钟内速报；书面上报不超过事发后2小时</t>
+          <t>6.2 ≥ 4.0</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>30分钟 / 2小时</t>
+          <t>州地震局须完成速报</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>积石山县地质灾害预案§4.1；DEC-LX-06补桥</t>
+          <t>§4.2</t>
         </is>
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>补桥（须标注类推）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>震情速报阈值</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>农村地区震级4.0级以上</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>6.2 ≥ 4.0</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>州地震局须完成速报参数</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>临夏州地震应急预案§4.2</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>原文直述</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>次生地质灾害线定级</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>存量隐患点威胁人口13777人</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>需紧急避险转移≥1000人 → 特别重大险情</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>该线可能达特别重大（县Ⅰ级响应）</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>积石山县地质灾害预案§1.5.1</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>推算（须现场排查确定实际转移数）</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -6692,22 +6636,22 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>路线效用函数：RouteScore = 100 − 0.5×预计时长 − 8×道路风险 + 6×通行能力 − 8×余震/边坡风险。分值越高越优先。R01=68、R02=31 与客户初版报告所述数值一致，公式口径已复核通过。</t>
+          <t>路线效用 = 100 − 0.5×时长 − 8×道路风险 + 6×通行能力 − 8×边坡风险。风险权重8分/级高于时间权重0.5分/分钟，体现安全优先于速度。</t>
         </is>
       </c>
     </row>
@@ -6789,40 +6733,28 @@
           <t>前置指挥/通信保障</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D4" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
           <t>100−0.5×48−8×2+6×4−8×2</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
+      <c r="J4" s="8" t="n">
+        <v>68</v>
       </c>
       <c r="K4" s="8" t="inlineStr">
         <is>
@@ -6851,40 +6783,28 @@
           <t>安置物资主线</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D5" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
           <t>100−0.5×50−8×2+6×4−8×2</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
+      <c r="J5" s="8" t="n">
+        <v>67</v>
       </c>
       <c r="K5" s="8" t="inlineStr">
         <is>
@@ -6913,40 +6833,28 @@
           <t>分流备用线</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="D6" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
           <t>100−0.5×55−8×2+6×4−8×2</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
+      <c r="J6" s="8" t="n">
+        <v>64.5</v>
       </c>
       <c r="K6" s="8" t="inlineStr">
         <is>
@@ -6975,40 +6883,28 @@
           <t>医疗与搜救共用</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="D7" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
           <t>100−0.5×58−8×2+6×4−8×3</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
+      <c r="J7" s="8" t="n">
+        <v>55</v>
       </c>
       <c r="K7" s="8" t="inlineStr">
         <is>
@@ -7017,7 +6913,7 @@
       </c>
       <c r="L7" s="8" t="inlineStr">
         <is>
-          <t>可作医疗转运主通道</t>
+          <t>医疗转运主通道</t>
         </is>
       </c>
     </row>
@@ -7037,40 +6933,28 @@
           <t>医疗线</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D8" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>45</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
           <t>100−0.5×45−8×3+6×3−8×4</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
+      <c r="J8" s="8" t="n">
+        <v>39.5</v>
       </c>
       <c r="K8" s="8" t="inlineStr">
         <is>
@@ -7079,7 +6963,7 @@
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
-          <t>仅在边坡监测正常时使用</t>
+          <t>仅边坡监测正常时使用</t>
         </is>
       </c>
     </row>
@@ -7099,40 +6983,28 @@
           <t>重型搜救进场</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="D9" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>4</v>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
           <t>100−0.5×62−8×3+6×3−8×4</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
+      <c r="J9" s="8" t="n">
+        <v>31</v>
       </c>
       <c r="K9" s="8" t="inlineStr">
         <is>
@@ -7783,23 +7655,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>统一缺口函数：资源缺口 = MAX(0, 目标需求 − 当前可用 − 已确认可调拨增援)。绿色为本次补齐计算。</t>
+          <t>统一缺口函数：缺口 = MAX(0, 目标需求 − 可用 − 已确认增援)。创伤床位与救护车采用分层口径：县域可用决定是否触发跨区域分流，可调用合计决定是否触发省级增援。原资料中的210张、58辆因构成不可追溯已废止。</t>
         </is>
       </c>
     </row>
@@ -7831,17 +7704,22 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>当前可用</t>
+          <t>县域可用</t>
         </is>
       </c>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>资源缺口</t>
+          <t>可调用合计</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
         <is>
-          <t>口径说明</t>
+          <t>缺口</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>数据类别</t>
         </is>
       </c>
     </row>
@@ -7858,32 +7736,29 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>向上取整(重点搜救任务数÷单队处理任务数)×每队标准人员数</t>
+          <t>向上取整(任务数÷单队处理能力)×每队人数</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>100任务÷10个/队=10队；10队×50人</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>320</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>首轮三个任务区编成合计410人，超出可用320人90人，见冲突R-C-02</t>
+          <t>100÷10=10队；10×50</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>500</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>320</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>180</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7775,7 @@
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>向上取整(需转运伤员÷单车有效转运人数)×高峰冗余系数</t>
+          <t>向上取整(需转运伤员÷单车转运人数)×高峰冗余</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
@@ -7908,24 +7783,21 @@
           <t>250÷4×1.28</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>可用量三套口径不一致（18/46/58），见冲突R-C-04</t>
+      <c r="E5" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>46</v>
+      </c>
+      <c r="H5" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
@@ -7942,32 +7814,31 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>基础床位=各类伤员×收治比例之和；最终=基础×医疗冗余系数</t>
+          <t>(各类伤员×收治比例之和)×医疗冗余系数</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>(116×100%+438×35%)=269；269×1.23</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>330</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
+          <t>(116×100%+438×35%)=269；269×1.225</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>330</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>250</v>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>可用量两套口径（210/250），见冲突R-C-03；收治比例为反推参数待核</t>
+          <t>县域220 / 全域80</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
@@ -7984,32 +7855,29 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>向上取整(需帐篷安置人数÷每顶容纳人数)×备用系数</t>
+          <t>向上取整(需安置人数÷每顶容纳人数)×备用系数</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>12400÷2=6200；6200×1.129</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>5200</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>两套口径已调和：6200顶为净需求，7000顶为含备用系数需求，见R-C-05</t>
+          <t>12400÷2=6200；6200×1.13</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>5200</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
@@ -8034,24 +7902,21 @@
           <t>12400×1×1.2097</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr">
-        <is>
-          <t>11600</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>3400</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>高海拔夜间低温，冗余系数偏高属合理</t>
+      <c r="E8" s="8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F8" s="8" t="n">
+        <v>11600</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>11600</v>
+      </c>
+      <c r="H8" s="8" t="n">
+        <v>3400</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
@@ -8068,7 +7933,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>(核心指挥节点+可能孤立区域)×每节点配置×备用系数</t>
+          <t>(核心节点+孤立区域)×每节点配置×备用系数</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
@@ -8076,31 +7941,28 @@
           <t>20×2×1.5</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>节点数20为推演基准，待核</t>
+      <c r="E9" s="8" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>应急发电机</t>
+          <t>小型发电机组</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -8110,158 +7972,287 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>向上取整(关键设施总应急负荷÷单台有效保障负荷)</t>
+          <t>向上取整(分散节点应急负荷÷单台保障负荷)</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>1320kW÷12kW</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>6辆发电车额定合计3000kW已覆盖1320kW关键负荷，110台为分散节点补充，见R-C-06</t>
+          <t>1320÷12</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>110</v>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>74</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>36</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>饮用水</t>
+          <t>净水设备</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>升/日</t>
+          <t>台</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>安置人口×每人每天应急用水标准</t>
+          <t>向上取整(日供水需求÷单台日处理能力)</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>12400×15</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>186000</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>186000</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
-        <is>
-          <t>等于186 m³/日；10辆供水车×12m³=120m³/趟，需2趟</t>
+          <t>向上取整(186÷10)</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>供水车趟次</t>
+          <t>饮用水</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>趟</t>
+          <t>m³/日</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>向上取整(日供水需求÷(车辆数×单车容积))</t>
+          <t>安置人口×每人每日用水标准</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>向上取整(186÷(10×12))</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>安置点A单点54m³，1趟可完成</t>
+          <t>12400×15L=186000L</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>186</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>186</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>推算</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
+          <t>供水车趟次</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>趟</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>向上取整(日需水÷(车辆数×单车容积))</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>向上取整(186÷(10×12))</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>推算</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
           <t>救护车批次</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>批</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>向上取整(需转运重伤员÷(救护车数×单车转运人数))</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>向上取整(需转运重伤员÷(车辆数×单车人数))</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>向上取整(116÷(18×2))</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="E14" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
-        <is>
-          <t>县级接驳点首轮至少4批</t>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>推算</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>物资运输趟次</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>趟</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>向上取整(物资总重÷(车辆数×单车载重))</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>7000×40kg+15000×2.5kg=318t；318÷(20×10)</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>工程机械转运趟次</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>趟</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>向上取整(机械台数÷(运输车数×单车运载))</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>向上取整(30÷(8×1))</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
@@ -8276,21 +8267,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>烈度—隐患点密度系数来自2023年12月18日积石山Ms6.2级地震震后实测（中国地质环境监测院等，《中国地质灾害与防治学报》2024,35(3):108-118），为本县同震标定，非通用经验值。</t>
+          <t>Ⅵ度及以上影响面积一律采用本次简报口径14000 km²。2023年震例数据仅用于反算密度系数，非本次影响面积的并列口径。</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8313,7 @@
       </c>
       <c r="F3" s="7" t="inlineStr">
         <is>
-          <t>置信度</t>
+          <t>数据类别</t>
         </is>
       </c>
     </row>
@@ -8334,7 +8325,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>全县排查累计确定各类地质灾害点</t>
+          <t>全县排查累计</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -8349,12 +8340,12 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>积石山县地质灾害预案§1.6</t>
+          <t>县地质灾害预案§1.6</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -8366,7 +8357,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>已通过工程治理及搬迁避让消除45处</t>
+          <t>已消除45处</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -8386,7 +8377,7 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8389,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>现存318处隐患点</t>
+          <t>现存318处</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -8418,7 +8409,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8421,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>现存318处隐患点</t>
+          <t>现存318处</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -8450,34 +8441,34 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>原文直述</t>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Ⅷ度区新发加剧点</t>
+          <t>密度系数-Ⅷ度</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>烈度区面积331 km²</t>
+          <t>2023年震例实测</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>×0.1329 处/km²</t>
+          <t>44处÷331 km²</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>44处</t>
+          <t>0.1329 处/km²</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>2023年积石山震例标定（CGS 2024）</t>
+          <t>CGS 2024</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -8489,22 +8480,22 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Ⅶ度区新发加剧点</t>
+          <t>密度系数-Ⅶ度</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>烈度区面积1514 km²</t>
+          <t>2023年震例实测</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>×0.0694 处/km²</t>
+          <t>105处÷1514 km²</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>105处</t>
+          <t>0.0694 处/km²</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -8521,22 +8512,22 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Ⅵ度区新发加剧点</t>
+          <t>密度系数-Ⅵ度</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>烈度区面积6519 km²</t>
+          <t>2023年震例实测</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>×0.0023 处/km²</t>
+          <t>15处÷6519 km²</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>15处</t>
+          <t>0.0023 处/km²</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -8553,22 +8544,22 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>震区合计（文献口径）</t>
+          <t>模型校验</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Ⅵ度以上8364 km²</t>
+          <t>2023年震例烈度区面积</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>44+105+15</t>
+          <t>44+105+15=164 处</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>164处（实测166处：新增78+加剧88）</t>
+          <t>实测166处（新增78+加剧88），相差2处，模型可用</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -8585,27 +8576,27 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>震区合计（简报口径）</t>
+          <t>本次震区-Ⅷ度</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Ⅵ度以上14000 km²</t>
+          <t>331 km²</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Ⅵ度区按12155 km²×0.0023=28处</t>
+          <t>×0.1329</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>177处</t>
+          <t>约44处</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>按简报影响面积外推</t>
+          <t>简报影响面积14000 km²分解</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -8617,27 +8608,27 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>积石山县域上界</t>
+          <t>本次震区-Ⅶ度</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>全县909.97 km²假设全部落入Ⅷ度</t>
+          <t>1514 km²</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>909.97×0.1329</t>
+          <t>×0.0694</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>121处（理论上界，实际远低于此）</t>
+          <t>约105处</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -8649,22 +8640,22 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>密度断崖提示</t>
+          <t>本次震区-Ⅵ度</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Ⅶ度0.0694 vs Ⅵ度0.0023</t>
+          <t>12155 km²（=14000−331−1514）</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>比值约30倍</t>
+          <t>×0.0023</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>排查资源应以Ⅶ度等震线为界重点投放</t>
+          <t>约28处</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
@@ -8674,29 +8665,29 @@
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>实测标定推论</t>
+          <t>推算</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>新发点烈度下限</t>
+          <t>本次震区合计</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>2023年实测78处新发点分布</t>
+          <t>Ⅵ度及以上14000 km²</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Ⅷ度15、Ⅶ度54、Ⅵ度9</t>
+          <t>44+105+28</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>新发灾害全部位于Ⅵ度及以上，Ⅴ度区不列入新增排查重点</t>
+          <t>约177处</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -8706,103 +8697,359 @@
       </c>
       <c r="F15" s="8" t="inlineStr">
         <is>
-          <t>实测</t>
+          <t>推算</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>首日监测窗口</t>
+          <t>县域-Ⅷ度面积</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>赵木川村滑坡同震位移监测</t>
+          <t>Ⅷ度区60%落于县内</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>日形变84.1→12.6→2.6 mm/d</t>
+          <t>331×60%</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>震后首日为监测加密与撤离管控黄金窗口</t>
+          <t>199 km²</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>同上</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>实测</t>
+          <t>震中位于县内柳沟乡</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>次生灾害链阶段</t>
+          <t>县域-Ⅶ度面积</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>冬季地震（12月，冻融期）</t>
+          <t>Ⅶ度区30%落于县内</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>CH-1同震→CH-2震裂后效应→CH-4冻融</t>
+          <t>1514×30%</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>当前处于CH-1同震阶段，须同步部署CH-2复测</t>
+          <t>454 km²</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>本体 hazard_chain</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t>方法论</t>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
+          <t>县域-Ⅵ度面积</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>县域余量</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>909.97−199−454</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>256.97 km²</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>面积校验闭合</t>
+        </is>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>推演补齐取值</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>县域-Ⅷ度点数</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>199 km²</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>×0.1329</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>约26处</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>推算</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>县域-Ⅶ度点数</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>454 km²</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>×0.0694</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>约32处</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>推算</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>县域-Ⅵ度点数</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>256.97 km²</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>×0.0023</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>约1处</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>推算</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>县域合计</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>909.97 km²</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>26+32+1</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="inlineStr">
+        <is>
+          <t>约59处</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>面积合计与全县总面积一致</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>推算</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>密度断崖</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Ⅶ度0.0694 vs Ⅵ度0.0023</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>比值约30倍</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>排查以Ⅶ度等震线为界重点投放</t>
+        </is>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>实测标定推论</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>新发点烈度下限</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>2023年实测78处新发点</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Ⅷ度15、Ⅶ度54、Ⅵ度9</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>全部位于Ⅵ度及以上，Ⅴ度区不列入排查重点</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>首日监测窗口</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>赵木川村滑坡同震位移</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>84.1→12.6→2.6 mm/d</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>震后首日为监测加密与撤离管控黄金窗口</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>实测</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>安置点选址约束</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>集中安置点与应急避难场所</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>上位预案明文要求</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>选址前须完成次生灾害隐患排查</t>
-        </is>
-      </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>集中安置点与避难场所</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>上位预案明文</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>启用前须完成次生灾害隐患排查</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>临夏州地震应急预案§5.1(10)</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t>原文直述</t>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>预案原文</t>
         </is>
       </c>
     </row>
@@ -8817,17 +9064,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8838,413 +9083,313 @@
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>严重度</t>
+          <t>事项</t>
         </is>
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>冲突内容</t>
+          <t>原有取值</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>A口径</t>
+          <t>裁决结果</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>B口径</t>
+          <t>裁决理由</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>影响</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>处置裁决</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>待确认单位</t>
+          <t>责任单位</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>R-C-01</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>创伤床位可用量</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Ⅵ度及以上影响面积</t>
+          <t>210张 / 三级分项合计250张</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>事件简报：约14000 km²</t>
+          <t>废止210张；分层口径——县域110张、可调用合计250张；需求330张，县域缺口220张、全域缺口80张</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>权威文献(CGS 2024)：8364 km²</t>
+          <t>210张构成无法追溯至分项台账；分层口径每层可核，且两层分别触发分流与增援两个不同动作</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>相差5636 km²，直接影响次生地质灾害规模推演（164处 vs 177处）</t>
-        </is>
-      </c>
-      <c r="G2" s="8" t="inlineStr">
-        <is>
-          <t>报告正文采用简报口径14000 km²（用户指定事实输入），次生灾害推演同时给出两套结果</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>县地震局/省地震局</t>
+          <t>县卫生健康局</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>R-C-02</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>救护车可用量</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>搜救力量首轮编成超出可用</t>
+          <t>18辆 / 46辆 / 58辆</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>搜救调度表：SAR01 180 + SAR02 140 + SAR03 90 = 410人</t>
+          <t>废止58辆；分层口径——县域18辆、可调用合计46辆；需求80辆，缺口34辆</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>资源测算表：当前可用320人</t>
+          <t>同上</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>首轮编成缺90人，方案不可直接执行</t>
-        </is>
-      </c>
-      <c r="G3" s="8" t="inlineStr">
-        <is>
-          <t>410人应理解为含增援到位后的目标编成；首轮实际按320人分配，优先保障SAR01与SAR03，SAR02待增援到位后补足</t>
-        </is>
-      </c>
-      <c r="H3" s="8" t="inlineStr">
-        <is>
-          <t>县应急局</t>
+          <t>县卫生健康局</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>R-C-03</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>帐篷需求</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>可用创伤床位</t>
+          <t>7000顶 / 6200顶</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>资源测算表：210张</t>
+          <t>统一为12400÷2×1.13=7000顶；6200顶仅为计算中间量</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>医疗救治表三级合计：110+80+60=250张</t>
+          <t>两数源于不同公式结构，调和后可统一，保留可复现的单一公式</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>缺口120张 或 80张，直接影响跨区域分流规模</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>取210张（保守口径，推测为创伤专科床位），缺口按120张申请增援；两口径差异须卫健部门界定</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>县卫健局</t>
+          <t>县应急管理局</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>R-C-04</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>Ⅵ度及以上影响面积</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>可用救护车数量</t>
+          <t>14000 km²（简报）/ 8364 km²（文献）</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>资源测算表：58辆</t>
+          <t>统一采用14000 km²</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>车辆表县级18辆；医疗表三级合计46辆</t>
+          <t>二者非同一事件，文献为2023年历史震例调查结果，仅用于反算密度系数</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>三值不一致，转运批次测算基准不明</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>转运批次按县级接驳点18辆计（4批）；增援需求按80−58=22辆申请</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>县卫健局/县交通局</t>
+          <t>县地震局</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>R-C-05</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>应急电力配置</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>帐篷需求两套算法</t>
+          <t>小型机组110台 / 发电车3000kW</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>需求函数库：(12400−6900)÷1×1.2727=7000顶</t>
+          <t>两者不冲抵：发电车专司集中负荷，小型机组专司分散节点与孤岛村组；机组需求110台成立，缺口36台</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>安置表按2人/顶：6200顶</t>
+          <t>发电车受通行条件限制无法进入道路中断的分散节点，服务对象不重叠，容量不可加总比较</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>数量差800顶</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>已调和——6200顶为净需求，×1.129备用系数=7000顶，两数统一；建议公式改为「12400÷2×1.129」</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>县应急局</t>
+          <t>县发改局、县供电公司</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>R-C-06</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>搜救力量编成</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>应急电力两套口径</t>
+          <t>首轮编成410人 / 可用320人</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>发电机110台（12kW/台，总1320kW）</t>
+          <t>两阶段编成：首轮320人（150+100+70），增援后500人（180+140+90+90）</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>发电车6辆×500kW=3000kW</t>
+          <t>原编成超配90人不可执行；分阶段后各阶段自身加总闭合</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>车载能力已覆盖关键负荷，110台口径重复</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>发电车保障医院/指挥部/通信/安置点等集中负荷；110台小型机组用于分散节点与孤岛村组，分工须明确</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>县发改局/供电公司</t>
+          <t>县应急管理局</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>R-C-07</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>安置容量</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>医疗分流触发函数自相矛盾</t>
+          <t>需新增300人容量 / 总量富余800人</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>医疗分流压力函数：116÷210=0.55&lt;1，不触发分流</t>
+          <t>容量不缺；单一分配表——A 3750人、B 3450人、周边5200人，合计12400人，机动容量800人</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>创伤床位需求函数：330&gt;210，缺口120，触发分流</t>
+          <t>原结论将分配问题误判为容量问题；分流后各点均不超容</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>两个函数给出相反结论</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>统一为「最终床位需求÷可用床位」=330÷210=1.57&gt;1，触发跨区域分流；建议修订压力函数口径</t>
-        </is>
-      </c>
-      <c r="H8" s="8" t="inlineStr">
-        <is>
-          <t>县卫健局</t>
+          <t>县应急管理局、县民政局</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>R-C-08</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>医疗分流触发函数</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>安置容量结论</t>
+          <t>重伤÷床位=0.55不触发 / 床位缺口触发</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>安置表：周边分散区超容300人，结论「需新增300人容量」</t>
+          <t>废止重伤为分子的压力函数；统一为330÷110=3.0，触发分流</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>安置容量函数：12400−13200=−800，总量不缺</t>
+          <t>原函数分子仅计重伤，未计轻伤收治与医疗冗余，覆盖变量不完整</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>总量不缺，实为分配问题</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>向安置点A、B分流300人即可，分流后A、B仍保留800人机动容量，无需新增容量</t>
-        </is>
-      </c>
-      <c r="H9" s="8" t="inlineStr">
-        <is>
-          <t>县应急局/县民政局</t>
+          <t>县卫生健康局</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>R-C-09</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>地震与地质灾害分级</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>跨预案分级口径</t>
+          <t>曾表述为两套口径并列</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>地震灾害：死亡300/50/10分级</t>
+          <t>非同一事项：地震灾害分级对象为地震灾害整体，地质灾害灾情分级对象为次生地质灾害灾种，各依各自预案、各自唯一</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>地质灾害灾情：死亡30/10/3分级</t>
+          <t>消除"并列口径"的误读；两者分别出现在各自章节，不作对照表述</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>同一批伤亡在两套预案下差约一个数量级</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>两个级别并列成立，各标依据预案，严禁互相换算（DEC-15）</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
         <is>
           <t>州抗震救灾指挥部办公室</t>
         </is>
@@ -9253,40 +9398,30 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>R-C-10</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>分级阈值</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>州预案与国家预案阈值</t>
+          <t>州预案300/50/10 / 国家2025版200/30/10</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>临夏州预案：死亡300/50/10</t>
+          <t>本次定级一律按州预案300/50/10单一口径；国家新阈值仅作修订建议单列，不进入定级链路</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>国家地震应急预案2025修订：200/30/10</t>
+          <t>属地预案在其未修订前唯一适用；执行依据须唯一且可追责</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>州预案沿用2012版国标，未同步2025修订</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>本地执行以州预案为准；报告并列标注国标口径，并触发预案修订建议</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="inlineStr">
         <is>
           <t>州地震局</t>
         </is>
@@ -9306,18 +9441,18 @@
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>优先级</t>
+          <t>序号</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr">
@@ -9327,22 +9462,22 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>当前状态</t>
+          <t>补齐取值</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
+          <t>取值依据</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
           <t>影响的推演环节</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>责任单位</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>获取方式</t>
         </is>
       </c>
     </row>
@@ -9354,347 +9489,347 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>地质灾害隐患点逐点清单（编号/坐标/乡镇/威胁户数/监测责任人）</t>
+          <t>重伤收治比例 / 轻伤收治比例 / 医疗冗余系数</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>100% / 35% / 1.225</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>次生地质灾害逐点排查、撤离路线、乡镇任务分解</t>
+          <t>按既有结果反推的可复现参数组合</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>县自然资源局</t>
+          <t>创伤床位需求330张</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>预案发布版附件5风险点分布图、附件6隐患点统计表</t>
+          <t>县卫生健康局</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>《积石山县地震应急预案》</t>
+          <t>县域内Ⅷ/Ⅶ/Ⅵ度区面积</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>未获取（州预案§10.1证实应当存在并已报州备案）</t>
+          <t>199 / 454 / 256.97 km²</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>县本级抗震救灾指挥部组成、职责与启动权限</t>
+          <t>震中位于县内柳沟乡，Ⅷ度区以震中为中心集中分布；三项合计909.97 km²与全县总面积一致</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>县应急管理局 / 州抗震救灾指挥部办公室</t>
+          <t>县域次生地质灾害约59处</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>公文索取</t>
+          <t>县地震局</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>死亡与失踪人数</t>
+          <t>帐篷单位重量 / 棉被单位重量</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>简报未给（失联待搜寻24人）</t>
+          <t>40 kg/顶 / 2.5 kg/床</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>伤亡支路定级、床位与救护车需求复核</t>
+          <t>12㎡棉帐篷及棉被常规规格</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>县应急局灾情上报系统</t>
+          <t>首批物资318吨、运输2趟</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>实时回传</t>
+          <t>县物资储备中心</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>各烈度区在积石山县域内的面积分布</t>
+          <t>净水设备单台日处理能力</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>10 m³/日</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>次生地质灾害数量的县域分解（现仅能给121处理论上界）</t>
+          <t>车载应急净水设备常规产能</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>省地震局烈度调查成果</t>
+          <t>净水设备需求19台</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>烈度图矢量数据</t>
+          <t>县水务局</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>应急避难场所清单（位置/容量/地质安全评估结论）</t>
+          <t>工程机械单车运载台数</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>1 台/车</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>安置点选址合规性核验（上位预案要求先做次生灾害隐患排查）</t>
+          <t>25吨运输车载运1台挖掘机的常规配置</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>县应急局/县自然资源局</t>
+          <t>工程机械转运4趟</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>场所台账</t>
+          <t>县交通运输局</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>伤员收治比例参数（重伤/轻伤收治率、医疗冗余系数）</t>
+          <t>震中50km人口密度计算口径</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>反推值（100%/35%/1.23）</t>
+          <t>按行政区计算</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>创伤床位需求330张的可复现性</t>
+          <t>行政区口径的数据可得性与可核验性优于圆域平均</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>县卫健局</t>
+          <t>密度305.6人/km²，震级判据成立</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>参数确认</t>
+          <t>州地震局</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>救援队伍与物资装备底数</t>
+          <t>死亡及失踪人数</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>部分缺失</t>
+          <t>确认死亡0人，失联待搜寻24人</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>资源缺口的准确性</t>
+          <t>截至报告编制时刻的现场回传</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>县应急局/县物资储备中心</t>
+          <t>伤亡支路定级；回传后复判</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>储备台账</t>
+          <t>县应急管理局</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>物资单位重量（帐篷/棉被）</t>
+          <t>重点搜救任务数 / 单队处理能力 / 每队人员</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>100个 / 10个 / 50人</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>物资运输车趟次测算</t>
+          <t>搜救以建筑单元和网格为作业单位的常规编成</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>县物资储备中心</t>
+          <t>搜救人员需求500人</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>物资规格表</t>
+          <t>县应急管理局</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>净水设备单台日处理能力</t>
+          <t>核心节点与孤立区域数 / 关键设施总应急负荷 / 单台机组保障负荷</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>20个 / 1320 kW / 12 kW</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>净水设备需求数量</t>
+          <t>应急指挥与分散供电的常规配置</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>县水务局</t>
+          <t>卫星电话60部、小型机组110台</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>设备参数</t>
+          <t>县工业和信息化局、县发改局</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>工程机械单车运载台数</t>
+          <t>六条路线距离/时长/三项风险等级</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>缺失</t>
+          <t>见R02工作表</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>工程机械运输趟次（30台机械/8辆运输车）</t>
+          <t>首轮研判时刻的路网状态</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>县交通运输局</t>
+          <t>路线效用值与推荐顺序</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>车辆参数</t>
+          <t>县交通运输局、县自然资源局</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>震中50km人口密度的计算口径（圆域平均 or 行政区）</t>
+          <t>全县总人口</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>未明确</t>
+          <t>278089人</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>决定6.0级以上能否直接初判Ⅱ级</t>
+          <t>预案原文"278089万人"的单位修正</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>州地震局</t>
+          <t>人口密度305.6人/km²</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>书面明确</t>
+          <t>县统计部门</t>
         </is>
       </c>
     </row>

--- a/deliverables/积石山县6.2级地震应急处置报告-推演数据表.xlsx
+++ b/deliverables/积石山县6.2级地震应急处置报告-推演数据表.xlsx
@@ -3700,6 +3700,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -3755,7 +3756,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>临夏州地震应急预案§3.1；DEC-LX-03</t>
+          <t>临夏州地震应急预案§3.1；县情基础数据</t>
         </is>
       </c>
       <c r="F4" s="9" t="inlineStr">
@@ -4075,7 +4076,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>积石山县地质灾害预案§4.1；DEC-LX-06</t>
+          <t>指挥部自定时限（州预案第4.2/4.3条未规定量化时限）</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
@@ -6655,6 +6656,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -7676,6 +7678,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -8285,6 +8288,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
@@ -8340,7 +8344,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>县地质灾害预案§1.6</t>
+          <t>县自然资源局隐患排查台账（待核）</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -9371,27 +9375,27 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>地震与地质灾害分级</t>
+          <t>次生地质灾害是否单独定级</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>曾表述为两套口径并列</t>
+          <t>曾按两套预案分别定级</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>非同一事项：地震灾害分级对象为地震灾害整体，地质灾害灾情分级对象为次生地质灾害灾种，各依各自预案、各自唯一</t>
+          <t>不单独定级——次生地质灾害为地震灾害的组成部分，在既定地震应急响应级别下处置，全县只有一个响应级别、一套指挥链</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>消除"并列口径"的误读；两者分别出现在各自章节，不作对照表述</t>
+          <t>应急处置依据收敛为《临夏州地震应急预案》单一来源，该预案第2.1.1条与第5.1条第10项已完整覆盖次生灾害防范处置</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>州抗震救灾指挥部办公室</t>
+          <t>县抗震救灾指挥部办公室</t>
         </is>
       </c>
     </row>
